--- a/tame_output/ON/bt/strategyON_20231113.xlsx
+++ b/tame_output/ON/bt/strategyON_20231113.xlsx
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>132.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1375,11 +1375,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1779"/>
+  <dimension ref="A1:G1780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.132941896896311</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42443,6 +42443,29 @@
       </c>
       <c r="G1779" t="n">
         <v>4.37336116254848</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="2" t="n">
+        <v>45242</v>
+      </c>
+      <c r="B1780" t="n">
+        <v>3.132571069090908</v>
+      </c>
+      <c r="C1780" t="n">
+        <v>3.065147691018159</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>1.547579820343774</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>3.683823194841922</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>2.177212046409986</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>4.371474918864152</v>
       </c>
     </row>
   </sheetData>
